--- a/FS20_HudBar/Config/EngineMerge.xlsx
+++ b/FS20_HudBar/Config/EngineMerge.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5374" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5415" uniqueCount="325">
   <si>
     <t>ACFT</t>
   </si>
@@ -990,6 +990,9 @@
   </si>
   <si>
     <t>H_COLL_LEV</t>
+  </si>
+  <si>
+    <t>FLAPS_VOICE</t>
   </si>
 </sst>
 </file>
@@ -7689,17 +7692,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:FJ41"/>
+  <dimension ref="A1:FK41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="75" width="3.7109375" bestFit="1" customWidth="1"/>
     <col min="76" max="77" width="3.7109375" customWidth="1"/>
     <col min="78" max="86" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="87" max="165" width="3.7109375" customWidth="1"/>
-    <col min="166" max="166" width="36.28515625" customWidth="1"/>
+    <col min="87" max="166" width="3.7109375" customWidth="1"/>
+    <col min="167" max="167" width="36.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:166" s="11" customFormat="1" ht="75.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:167" s="11" customFormat="1" ht="75.75" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>95</v>
       </c>
@@ -8193,13 +8196,16 @@
         <v>323</v>
       </c>
       <c r="FI1" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="FJ1" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="FJ1" t="s">
+      <c r="FK1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>88</v>
       </c>
@@ -8731,14 +8737,17 @@
         <v>0</v>
       </c>
       <c r="FI2" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ2" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ2" t="str">
+      <c r="FK2" t="str">
         <f>Tabelle1!AV2</f>
         <v>Airbus A320 Neo</v>
       </c>
     </row>
-    <row r="3" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>88</v>
       </c>
@@ -9270,14 +9279,17 @@
         <v>0</v>
       </c>
       <c r="FI3" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ3" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ3" t="str">
+      <c r="FK3" t="str">
         <f>Tabelle1!AV3</f>
         <v>Boeing 747-8i</v>
       </c>
     </row>
-    <row r="4" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>88</v>
       </c>
@@ -9809,14 +9821,17 @@
         <v>0</v>
       </c>
       <c r="FI4" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ4" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ4" t="str">
+      <c r="FK4" t="str">
         <f>Tabelle1!AV4</f>
         <v>Boeing 787-10</v>
       </c>
     </row>
-    <row r="5" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>88</v>
       </c>
@@ -10348,14 +10363,17 @@
         <v>0</v>
       </c>
       <c r="FI5" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ5" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ5" t="str">
+      <c r="FK5" t="str">
         <f>Tabelle1!AV5</f>
         <v>Boeing F/A 18E Super Hornet</v>
       </c>
     </row>
-    <row r="6" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>88</v>
       </c>
@@ -10887,14 +10905,17 @@
         <v>0</v>
       </c>
       <c r="FI6" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ6" t="str">
+      <c r="FK6" t="str">
         <f>Tabelle1!AV6</f>
         <v>Baron G58</v>
       </c>
     </row>
-    <row r="7" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>88</v>
       </c>
@@ -11426,14 +11447,17 @@
         <v>0</v>
       </c>
       <c r="FI7" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ7" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ7" t="str">
+      <c r="FK7" t="str">
         <f>Tabelle1!AV7</f>
         <v>Bonanza G36</v>
       </c>
     </row>
-    <row r="8" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>88</v>
       </c>
@@ -11965,14 +11989,17 @@
         <v>0</v>
       </c>
       <c r="FI8" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ8" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ8" t="str">
+      <c r="FK8" t="str">
         <f>Tabelle1!AV8</f>
         <v>Beechcraft King Air 350i</v>
       </c>
     </row>
-    <row r="9" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>88</v>
       </c>
@@ -12504,14 +12531,17 @@
         <v>0</v>
       </c>
       <c r="FI9" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ9" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ9" t="str">
+      <c r="FK9" t="str">
         <f>Tabelle1!AV9</f>
         <v>Cessna 152</v>
       </c>
     </row>
-    <row r="10" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>88</v>
       </c>
@@ -13043,14 +13073,17 @@
         <v>0</v>
       </c>
       <c r="FI10" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ10" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ10" t="str">
+      <c r="FK10" t="str">
         <f>Tabelle1!AV10</f>
         <v>Cessna 152 Aero</v>
       </c>
     </row>
-    <row r="11" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>88</v>
       </c>
@@ -13582,14 +13615,17 @@
         <v>0</v>
       </c>
       <c r="FI11" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ11" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ11" t="str">
+      <c r="FK11" t="str">
         <f>Tabelle1!AV11</f>
         <v>Cessna 172sp Skyhawk G1000</v>
       </c>
     </row>
-    <row r="12" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>88</v>
       </c>
@@ -14121,14 +14157,17 @@
         <v>0</v>
       </c>
       <c r="FI12" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ12" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ12" t="str">
+      <c r="FK12" t="str">
         <f>Tabelle1!AV12</f>
         <v>Cessna 172sp Skyhawk</v>
       </c>
     </row>
-    <row r="13" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>88</v>
       </c>
@@ -14660,14 +14699,17 @@
         <v>0</v>
       </c>
       <c r="FI13" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ13" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ13" t="str">
+      <c r="FK13" t="str">
         <f>Tabelle1!AV13</f>
         <v>Cessna 208B Grand Caravan EX</v>
       </c>
     </row>
-    <row r="14" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>88</v>
       </c>
@@ -15199,14 +15241,17 @@
         <v>0</v>
       </c>
       <c r="FI14" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ14" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ14" t="str">
+      <c r="FK14" t="str">
         <f>Tabelle1!AV14</f>
         <v>Cessna CJ4 Citation</v>
       </c>
     </row>
-    <row r="15" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>88</v>
       </c>
@@ -15738,14 +15783,17 @@
         <v>0</v>
       </c>
       <c r="FI15" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ15" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ15" t="str">
+      <c r="FK15" t="str">
         <f>Tabelle1!AV15</f>
         <v>Cessna Longitude</v>
       </c>
     </row>
-    <row r="16" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>88</v>
       </c>
@@ -16277,14 +16325,17 @@
         <v>0</v>
       </c>
       <c r="FI16" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ16" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ16" t="str">
+      <c r="FK16" t="str">
         <f>Tabelle1!AV16</f>
         <v>DA40-NG</v>
       </c>
     </row>
-    <row r="17" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>88</v>
       </c>
@@ -16816,14 +16867,17 @@
         <v>0</v>
       </c>
       <c r="FI17" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ17" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ17" t="str">
+      <c r="FK17" t="str">
         <f>Tabelle1!AV17</f>
         <v>DA40 TDI</v>
       </c>
     </row>
-    <row r="18" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>88</v>
       </c>
@@ -17355,14 +17409,17 @@
         <v>0</v>
       </c>
       <c r="FI18" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ18" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ18" t="str">
+      <c r="FK18" t="str">
         <f>Tabelle1!AV18</f>
         <v>DA62</v>
       </c>
     </row>
-    <row r="19" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>88</v>
       </c>
@@ -17894,14 +17951,17 @@
         <v>0</v>
       </c>
       <c r="FI19" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ19" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ19" t="str">
+      <c r="FK19" t="str">
         <f>Tabelle1!AV19</f>
         <v>DR400</v>
       </c>
     </row>
-    <row r="20" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>88</v>
       </c>
@@ -18433,14 +18493,17 @@
         <v>0</v>
       </c>
       <c r="FI20" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ20" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ20" t="str">
+      <c r="FK20" t="str">
         <f>Tabelle1!AV20</f>
         <v>DV20</v>
       </c>
     </row>
-    <row r="21" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>88</v>
       </c>
@@ -18972,14 +19035,17 @@
         <v>0</v>
       </c>
       <c r="FI21" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ21" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ21" t="str">
+      <c r="FK21" t="str">
         <f>Tabelle1!AV21</f>
         <v>Extra 330</v>
       </c>
     </row>
-    <row r="22" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>88</v>
       </c>
@@ -19511,14 +19577,17 @@
         <v>0</v>
       </c>
       <c r="FI22" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ22" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ22" t="str">
+      <c r="FK22" t="str">
         <f>Tabelle1!AV22</f>
         <v>FlightDesignCT</v>
       </c>
     </row>
-    <row r="23" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>88</v>
       </c>
@@ -20050,14 +20119,17 @@
         <v>0</v>
       </c>
       <c r="FI23" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ23" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ23" t="str">
+      <c r="FK23" t="str">
         <f>Tabelle1!AV23</f>
         <v>Icon A5</v>
       </c>
     </row>
-    <row r="24" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>88</v>
       </c>
@@ -20589,14 +20661,17 @@
         <v>0</v>
       </c>
       <c r="FI24" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ24" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ24" t="str">
+      <c r="FK24" t="str">
         <f>Tabelle1!AV24</f>
         <v>Mudry Cap 10 C</v>
       </c>
     </row>
-    <row r="25" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>88</v>
       </c>
@@ -21128,14 +21203,17 @@
         <v>0</v>
       </c>
       <c r="FI25" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ25" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ25" t="str">
+      <c r="FK25" t="str">
         <f>Tabelle1!AV25</f>
         <v>Pilatus PC-6 Gauge</v>
       </c>
     </row>
-    <row r="26" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>88</v>
       </c>
@@ -21667,14 +21745,17 @@
         <v>0</v>
       </c>
       <c r="FI26" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ26" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ26" t="str">
+      <c r="FK26" t="str">
         <f>Tabelle1!AV26</f>
         <v>Pilatus PC-6 G950</v>
       </c>
     </row>
-    <row r="27" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>88</v>
       </c>
@@ -22206,14 +22287,17 @@
         <v>0</v>
       </c>
       <c r="FI27" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ27" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ27" t="str">
+      <c r="FK27" t="str">
         <f>Tabelle1!AV27</f>
         <v>Pipistrel Alpha Electro</v>
       </c>
     </row>
-    <row r="28" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>88</v>
       </c>
@@ -22745,14 +22829,17 @@
         <v>0</v>
       </c>
       <c r="FI28" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ28" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ28" t="str">
+      <c r="FK28" t="str">
         <f>Tabelle1!AV28</f>
         <v>Pitts Special 1S</v>
       </c>
     </row>
-    <row r="29" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>88</v>
       </c>
@@ -23284,14 +23371,17 @@
         <v>0</v>
       </c>
       <c r="FI29" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ29" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ29" t="str">
+      <c r="FK29" t="str">
         <f>Tabelle1!AV29</f>
         <v>Pitts Special S2S</v>
       </c>
     </row>
-    <row r="30" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>88</v>
       </c>
@@ -23823,14 +23913,17 @@
         <v>0</v>
       </c>
       <c r="FI30" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ30" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ30" t="str">
+      <c r="FK30" t="str">
         <f>Tabelle1!AV30</f>
         <v>Savage Cub</v>
       </c>
     </row>
-    <row r="31" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>88</v>
       </c>
@@ -24362,14 +24455,17 @@
         <v>0</v>
       </c>
       <c r="FI31" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ31" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ31" t="str">
+      <c r="FK31" t="str">
         <f>Tabelle1!AV31</f>
         <v>Savage Shock Ultra</v>
       </c>
     </row>
-    <row r="32" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>88</v>
       </c>
@@ -24901,14 +24997,17 @@
         <v>0</v>
       </c>
       <c r="FI32" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ32" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ32" t="str">
+      <c r="FK32" t="str">
         <f>Tabelle1!AV32</f>
         <v>SR22</v>
       </c>
     </row>
-    <row r="33" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>88</v>
       </c>
@@ -25440,14 +25539,17 @@
         <v>0</v>
       </c>
       <c r="FI33" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ33" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ33" t="str">
+      <c r="FK33" t="str">
         <f>Tabelle1!AV33</f>
         <v>TBM 930</v>
       </c>
     </row>
-    <row r="34" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>88</v>
       </c>
@@ -25979,14 +26081,17 @@
         <v>0</v>
       </c>
       <c r="FI34" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ34" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ34" t="str">
+      <c r="FK34" t="str">
         <f>Tabelle1!AV34</f>
         <v>Vertigo</v>
       </c>
     </row>
-    <row r="35" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
         <v>88</v>
       </c>
@@ -26518,14 +26623,17 @@
         <v>0</v>
       </c>
       <c r="FI35" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ35" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ35" t="str">
+      <c r="FK35" t="str">
         <f>Tabelle1!AV35</f>
         <v>VL3</v>
       </c>
     </row>
-    <row r="36" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
         <v>88</v>
       </c>
@@ -27057,14 +27165,17 @@
         <v>0</v>
       </c>
       <c r="FI36" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ36" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ36" t="str">
+      <c r="FK36" t="str">
         <f>Tabelle1!AV36</f>
         <v>Volocity</v>
       </c>
     </row>
-    <row r="37" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>88</v>
       </c>
@@ -27596,14 +27707,17 @@
         <v>0</v>
       </c>
       <c r="FI37" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ37" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ37" t="str">
+      <c r="FK37" t="str">
         <f>Tabelle1!AV37</f>
         <v>NXCub</v>
       </c>
     </row>
-    <row r="38" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>88</v>
       </c>
@@ -28135,14 +28249,17 @@
         <v>0</v>
       </c>
       <c r="FI38" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ38" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ38" t="str">
+      <c r="FK38" t="str">
         <f>Tabelle1!AV38</f>
         <v>XCub</v>
       </c>
     </row>
-    <row r="39" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
         <v>88</v>
       </c>
@@ -28674,14 +28791,17 @@
         <v>0</v>
       </c>
       <c r="FI39" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ39" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ39" t="str">
+      <c r="FK39" t="str">
         <f>Tabelle1!AV39</f>
         <v>SWS Kodiak 100 II</v>
       </c>
     </row>
-    <row r="40" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>88</v>
       </c>
@@ -29213,14 +29333,17 @@
         <v>0</v>
       </c>
       <c r="FI40" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ40" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ40" t="str">
+      <c r="FK40" t="str">
         <f>Tabelle1!AV40</f>
         <v>Generic Glider</v>
       </c>
     </row>
-    <row r="41" spans="1:166" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:167" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>88</v>
       </c>
@@ -29752,9 +29875,12 @@
         <v>1</v>
       </c>
       <c r="FI41" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="FJ41" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="FJ41" t="str">
+      <c r="FK41" t="str">
         <f>Tabelle1!AV41</f>
         <v>Generic Heli Turbine</v>
       </c>
